--- a/Compositions calculations.xlsx
+++ b/Compositions calculations.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timur\Cheminformatics\Practice\CTAB-hydrotropes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T.Unusov\Jupyter_notebook\Misc\CTAB hydrotopes\CTAB-Hydrotropes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12440" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RandomForestRegressor" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -187,14 +187,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -210,9 +210,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,7 +250,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -322,7 +322,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,48 +473,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AI28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="9.140625" customWidth="1"/>
+    <col min="25" max="25" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="H1" s="7" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="H1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="M1" s="7" t="s">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="M1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="R1" s="7" t="s">
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="R1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="W1" s="7" t="s">
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="W1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="AE1" s="7" t="s">
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="AE1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -529,13 +529,13 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="W2" s="7" t="s">
+      <c r="W2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C3">
         <v>30</v>
       </c>
@@ -618,8 +618,8 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B4">
@@ -686,8 +686,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
       <c r="B5">
         <v>100</v>
       </c>
@@ -773,8 +773,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
       <c r="B6">
         <v>200</v>
       </c>
@@ -839,18 +839,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="C9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="C9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="C10">
         <v>30</v>
       </c>
@@ -864,8 +864,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B11">
@@ -932,8 +932,8 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
       <c r="B12">
         <v>100</v>
       </c>
@@ -1019,8 +1019,8 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
       <c r="B13">
         <v>200</v>
       </c>
@@ -1085,15 +1085,15 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="C17" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="C17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>30</v>
       </c>
@@ -1155,8 +1155,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B19">
@@ -1223,8 +1223,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
       <c r="B20">
         <v>100</v>
       </c>
@@ -1310,8 +1310,8 @@
         <v>260</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
       <c r="B21">
         <v>200</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B28">
         <f>B27/344</f>
         <v>0.14534883720930233</v>
@@ -1415,54 +1415,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1478,20 +1478,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>17</v>
       </c>
       <c r="B1">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1499,28 +1499,28 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1528,31 +1528,31 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9">
         <f>1000*((B7/1000)*B5)/B1</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10">
         <f>1000*((B7/1000)*B6)/B2</f>
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11">
         <f>B7-B9-B10</f>
-        <v>0.79999999999999982</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
